--- a/FinanceDataMigration/src/main/resources/migration-templates/CONTRACTOR.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/CONTRACTOR.xlsx
@@ -30,7 +30,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">ULB Name </t>
@@ -48,7 +47,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Contractor Name </t>
@@ -66,7 +64,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Correspondence Address </t>
@@ -87,7 +84,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Contact Person </t>
@@ -105,7 +101,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Mobile Number </t>
@@ -123,7 +118,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Email </t>
@@ -150,7 +144,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Bank Name </t>
@@ -168,7 +161,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Bank Branch </t>
@@ -186,7 +178,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">IFSC Code </t>
@@ -204,7 +195,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Bank Account Number </t>
@@ -222,7 +212,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Contractor Type </t>
@@ -240,7 +229,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Source </t>
@@ -261,7 +249,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Status </t>
@@ -279,7 +266,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">PAN Number </t>
@@ -359,28 +345,26 @@
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color indexed="2"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -429,22 +413,22 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -29050,25 +29034,8 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="6" disablePrompts="0">
-    <dataValidation sqref="P4:P998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$E$2:$E$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q4:Q998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$F$2:$F$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="M4:M998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'Bank Branch'!$D$4:$D$44</formula1>
-    </dataValidation>
-    <dataValidation sqref="B4:B998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="L4:L998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Bank!$C$4:$C$999</formula1>
-    </dataValidation>
-    <dataValidation sqref="S4:S998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$G$2:$G$5</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
